--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484841_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484841_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.155200000000001</v>
+        <v>8.171900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9127</v>
+        <v>7.7179</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2424</v>
+        <v>0.4541</v>
       </c>
       <c r="G2" t="n">
         <v>6.8298</v>
@@ -610,13 +610,13 @@
         <v>2.4531</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1652</v>
+        <v>-0.1484</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5008</v>
+        <v>0.3059</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.666</v>
+        <v>-0.4543</v>
       </c>
       <c r="V2" t="n">
         <v>0.9244</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7382</v>
+        <v>5.1981</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2823</v>
+        <v>3.7951</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4559</v>
+        <v>1.403</v>
       </c>
       <c r="G3" t="n">
         <v>1.7137</v>
@@ -688,13 +688,13 @@
         <v>1.887</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5526</v>
+        <v>0.0125</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.2241</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1586</v>
+        <v>-0.2116</v>
       </c>
       <c r="V3" t="n">
         <v>1.585</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3969</v>
+        <v>2.5305</v>
       </c>
       <c r="E4" t="n">
-        <v>2.907</v>
+        <v>3.1994</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5101</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>2.3169</v>
@@ -766,13 +766,13 @@
         <v>1.6983</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6748</v>
+        <v>-0.5412</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6343</v>
+        <v>-0.342</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0405</v>
+        <v>-0.1992</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3919</v>
+        <v>2.3667</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4867</v>
+        <v>0.779</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9052</v>
+        <v>1.5877</v>
       </c>
       <c r="G5" t="n">
         <v>1.6037</v>
@@ -844,13 +844,13 @@
         <v>2.0757</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0041</v>
+        <v>-0.0292</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1611</v>
+        <v>0.1312</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1571</v>
+        <v>-0.1604</v>
       </c>
       <c r="V5" t="n">
         <v>1.547</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7613</v>
+        <v>2.0801</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.889</v>
+        <v>-0.5967</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6503</v>
+        <v>2.6768</v>
       </c>
       <c r="G6" t="n">
         <v>2.9376</v>
@@ -922,13 +922,13 @@
         <v>1.6983</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9875</v>
+        <v>-0.6688</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6808</v>
+        <v>-0.3885</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3068</v>
+        <v>-0.2803</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4432</v>
+        <v>0.5935</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0046</v>
+        <v>0.102</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4386</v>
+        <v>0.4915</v>
       </c>
       <c r="G7" t="n">
         <v>0.0305</v>
@@ -1000,13 +1000,13 @@
         <v>0.5661</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1534</v>
+        <v>-0.0031</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0588</v>
+        <v>0.0386</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0946</v>
+        <v>-0.0417</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ORTOLA TOMAS</t>
+          <t>T. DESPLACE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0371</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2098</v>
+        <v>-3.2418</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1726</v>
+        <v>3.3342</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5363</v>
+        <v>-1.9301</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2584</v>
+        <v>-3.9474</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7947</v>
+        <v>2.0174</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6677</v>
+        <v>-3.0918</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6073</v>
+        <v>-3.7017</v>
       </c>
       <c r="L8" t="n">
-        <v>1.275</v>
+        <v>0.6099</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1315</v>
+        <v>1.1618</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6511</v>
+        <v>-0.2457</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5196</v>
+        <v>1.4075</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3774</v>
+        <v>1.887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2539</v>
+        <v>-0.1662</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.458</v>
+        <v>0.19</v>
       </c>
       <c r="U8" t="n">
-        <v>0.204</v>
+        <v>-0.3562</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6226</v>
+        <v>2.1886</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6226</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. CLOSSET MARTINEZ</t>
+          <t>J. ORTOLA TOMAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2505</v>
+        <v>0.0552</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3168</v>
+        <v>0.3072</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0663</v>
+        <v>-0.252</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5147</v>
+        <v>0.5363</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7615</v>
+        <v>-1.2584</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2468</v>
+        <v>1.7947</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8618</v>
+        <v>0.6677</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6973</v>
+        <v>-0.6073</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1645</v>
+        <v>1.275</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3471</v>
+        <v>-0.1315</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.6511</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4113</v>
+        <v>0.5196</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3774</v>
+        <v>0.3774</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5661</v>
+        <v>0.3774</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4068</v>
+        <v>-0.2359</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2352</v>
+        <v>-0.3605</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1716</v>
+        <v>0.1247</v>
       </c>
       <c r="V9" t="n">
-        <v>0.019</v>
+        <v>-0.6226</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.019</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. DESPLACE</t>
+          <t>D. CLOSSET MARTINEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2793</v>
+        <v>-0.0208</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5342</v>
+        <v>-0.2194</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2548</v>
+        <v>0.1986</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9301</v>
+        <v>0.5147</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.9474</v>
+        <v>0.7615</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0174</v>
+        <v>-0.2468</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.0918</v>
+        <v>0.8618</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.7017</v>
+        <v>0.6973</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6099</v>
+        <v>0.1645</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1618</v>
+        <v>-0.3471</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2457</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4075</v>
+        <v>-0.4113</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R10" t="n">
-        <v>1.887</v>
+        <v>0.5661</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5379</v>
+        <v>-0.1771</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1023</v>
+        <v>-0.1377</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4355</v>
+        <v>-0.0394</v>
       </c>
       <c r="V10" t="n">
-        <v>2.1886</v>
+        <v>0.019</v>
       </c>
       <c r="W10" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7349</v>
+        <v>-0.3813</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6484</v>
+        <v>-0.4535</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08649999999999999</v>
+        <v>0.0722</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4292</v>
@@ -1312,13 +1312,13 @@
         <v>0.3774</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6831</v>
+        <v>-0.3295</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3992</v>
+        <v>-0.2043</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2839</v>
+        <v>-0.1252</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1167</v>
+        <v>-4.1439</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4871</v>
+        <v>-3.4615</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.6824</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2779</v>
@@ -1390,13 +1390,13 @@
         <v>1.5096</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1804</v>
+        <v>0.1531</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3144</v>
+        <v>0.34</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.134</v>
+        <v>-0.1869</v>
       </c>
       <c r="V12" t="n">
         <v>1.2452</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.5424</v>
+        <v>16.5423</v>
       </c>
       <c r="E13" t="n">
-        <v>7.927599999999998</v>
+        <v>7.927699999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>8.614800000000001</v>
+        <v>8.614800000000002</v>
       </c>
       <c r="G13" t="n">
         <v>10.846</v>
@@ -1450,13 +1450,13 @@
         <v>7.4659</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.702299999999999</v>
+        <v>-3.7023</v>
       </c>
       <c r="N13" t="n">
         <v>-7.8179</v>
       </c>
       <c r="O13" t="n">
-        <v>4.115599999999999</v>
+        <v>4.1156</v>
       </c>
       <c r="P13" t="n">
         <v>0.9435000000000002</v>
@@ -1468,13 +1468,13 @@
         <v>15.096</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1337</v>
+        <v>-2.1338</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2032999999999996</v>
+        <v>-0.2031999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.9304</v>
+        <v>-1.9305</v>
       </c>
       <c r="V13" t="n">
         <v>6.8866</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9243</v>
+        <v>5.2425</v>
       </c>
       <c r="E14" t="n">
-        <v>7.4933</v>
+        <v>5.1549</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.569</v>
+        <v>0.0876</v>
       </c>
       <c r="G14" t="n">
         <v>2.9503</v>
@@ -1546,13 +1546,13 @@
         <v>2.2644</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9738</v>
+        <v>1.292</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2906</v>
+        <v>0.9522</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3168</v>
+        <v>0.3399</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3208</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2804</v>
+        <v>2.2247</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0399</v>
+        <v>1.7219</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2405</v>
+        <v>0.5027</v>
       </c>
       <c r="G15" t="n">
         <v>1.1943</v>
@@ -1624,13 +1624,13 @@
         <v>2.0757</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7254</v>
+        <v>0.2188</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9159</v>
+        <v>-0.2339</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1905</v>
+        <v>0.4527</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2642</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0476</v>
+        <v>-0.0257</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2717</v>
+        <v>-0.3691</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3193</v>
+        <v>0.3434</v>
       </c>
       <c r="G16" t="n">
         <v>1.2604</v>
@@ -1702,13 +1702,13 @@
         <v>0.9435</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3533</v>
+        <v>0.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1916</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1617</v>
+        <v>0.1858</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6226</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. BLASCO NAVARRO</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3401</v>
+        <v>-2.1718</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.5693</v>
+        <v>0.5493</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2292</v>
+        <v>-2.721</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3984</v>
+        <v>-2.4792</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.8142</v>
+        <v>-1.4118</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4158</v>
+        <v>-1.0674</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3085</v>
+        <v>0.5496</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.0489</v>
+        <v>1.141</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7403</v>
+        <v>-0.5914</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0899</v>
+        <v>-3.0288</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7654</v>
+        <v>-2.5528</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3245</v>
+        <v>-0.476</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6983</v>
+        <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5113</v>
+        <v>-0.2778</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2679</v>
+        <v>-0.0004</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2434</v>
+        <v>-0.2774</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3208</v>
+        <v>-0.9244</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6226</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>D. CALERO BAUTISTA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1726</v>
+        <v>-2.4817</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4251</v>
+        <v>-2.2782</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7475</v>
+        <v>-0.2036</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4792</v>
+        <v>-1.4546</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4118</v>
+        <v>0.4093</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0674</v>
+        <v>-1.8639</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5496</v>
+        <v>-1.384</v>
       </c>
       <c r="K18" t="n">
-        <v>1.141</v>
+        <v>-0.126</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5914</v>
+        <v>-1.258</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.0288</v>
+        <v>-0.0706</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.5528</v>
+        <v>0.5353</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.476</v>
+        <v>-0.6059</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5096</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5096</v>
+        <v>0.9435</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2786</v>
+        <v>0.2181</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9747</v>
+        <v>0.0493</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3039</v>
+        <v>0.1687</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9244</v>
+        <v>-1.2452</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9244</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CALERO BAUTISTA</t>
+          <t>L. BLASCO NAVARRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.29</v>
+        <v>-2.4826</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6679</v>
+        <v>-3.1539</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6221</v>
+        <v>0.6713</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4546</v>
+        <v>-2.3984</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4093</v>
+        <v>-2.8142</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8639</v>
+        <v>0.4158</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.384</v>
+        <v>-1.3085</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.126</v>
+        <v>-2.0489</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.258</v>
+        <v>0.7403</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0706</v>
+        <v>-1.0899</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5353</v>
+        <v>-0.7654</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6059</v>
+        <v>-0.3245</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5901999999999999</v>
+        <v>1.3688</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3404</v>
+        <v>0.6833</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2498</v>
+        <v>0.6855</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2452</v>
+        <v>-0.3208</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2452</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0028</v>
+        <v>-3.2799</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7545</v>
+        <v>-1.2674</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2482</v>
+        <v>-2.0125</v>
       </c>
       <c r="G20" t="n">
         <v>-1.934</v>
@@ -2014,13 +2014,13 @@
         <v>2.0757</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0688</v>
+        <v>0.6541</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2076</v>
+        <v>0.2796</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1388</v>
+        <v>0.3745</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2452</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>C. CAMPILLOS ALONSO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.8513</v>
+        <v>-6.1143</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4091</v>
+        <v>-4.3683</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4422</v>
+        <v>-1.7461</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.1242</v>
+        <v>-3.8607</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3359</v>
+        <v>-0.8061</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7883</v>
+        <v>-3.0547</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3078</v>
+        <v>-1.7698</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0994</v>
+        <v>0.1377</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2083</v>
+        <v>-1.9076</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8165</v>
+        <v>-2.0909</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2365</v>
+        <v>-0.9438</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.58</v>
+        <v>-1.1471</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0757</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.774</v>
+        <v>-1.887</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6983</v>
+        <v>0.9435</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3486</v>
+        <v>-0.3667</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3709</v>
+        <v>-0.0699</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0223</v>
+        <v>-0.2968</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.9434</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3018</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X21" t="n">
         <v>-0.3018</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. CAMPILLOS ALONSO</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.1379</v>
+        <v>-6.1544</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.0503</v>
+        <v>-4.604</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0876</v>
+        <v>-1.5504</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.8607</v>
+        <v>-4.1242</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8061</v>
+        <v>-1.3359</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.0547</v>
+        <v>-2.7883</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7698</v>
+        <v>-1.3078</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1377</v>
+        <v>-0.0994</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9076</v>
+        <v>-1.2083</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0909</v>
+        <v>-2.8165</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9438</v>
+        <v>-1.2365</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1471</v>
+        <v>-1.58</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9435</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.887</v>
+        <v>-3.774</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3903</v>
+        <v>0.0455</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7519</v>
+        <v>0.176</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6384</v>
+        <v>-0.1305</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9434</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.3018</v>
       </c>
       <c r="X22" t="n">
         <v>-0.3018</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-16.5424</v>
+        <v>-15.2432</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.614699999999999</v>
+        <v>-8.614800000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.927600000000001</v>
+        <v>-6.6286</v>
       </c>
       <c r="G23" t="n">
         <v>-10.8461</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7355999999999996</v>
+        <v>0.7355999999999998</v>
       </c>
       <c r="I23" t="n">
         <v>-11.5816</v>
@@ -2224,7 +2224,7 @@
         <v>3.702199999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>7.817899999999999</v>
+        <v>7.8179</v>
       </c>
       <c r="L23" t="n">
         <v>-4.1158</v>
@@ -2248,13 +2248,13 @@
         <v>14.1525</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1337</v>
+        <v>3.4328</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9305</v>
+        <v>1.9304</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2031999999999999</v>
+        <v>1.5024</v>
       </c>
       <c r="V23" t="n">
         <v>-6.8866</v>
